--- a/owners.xlsx
+++ b/owners.xlsx
@@ -330,12 +330,15 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="ResidentsTable" displayName="ResidentsTable" ref="A3:C23" headerRowCount="1">
-  <x:autoFilter ref="A3:C23"/>
-  <x:tableColumns count="3">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="OwnersTable" displayName="OwnersTable" ref="A3:F23" headerRowCount="1">
+  <x:autoFilter ref="A3:F23"/>
+  <x:tableColumns count="6">
     <x:tableColumn id="1" name="דירה"/>
     <x:tableColumn id="2" name="שם"/>
     <x:tableColumn id="3" name="טלפון"/>
+    <x:tableColumn id="4" name="עיסוק"/>
+    <x:tableColumn id="5" name="איש/אשת קשר נוסף/ת"/>
+    <x:tableColumn id="6" name="טלפון נוסף"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showRowStripes="1"/>
 </x:table>
@@ -533,12 +536,15 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<x:worksheet xmlns:ns1="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="11" hidden="0" customWidth="1"/>
     <x:col min="2" max="2" width="34" hidden="0" customWidth="1"/>
     <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="26" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="20" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="34" customHeight="1">
@@ -547,6 +553,9 @@
       </x:c>
       <x:c r="B1" s="4"/>
       <x:c r="C1" s="4"/>
+      <x:c r="D1" s="4"/>
+      <x:c r="E1" s="4"/>
+      <x:c r="F1" s="4"/>
     </x:row>
     <x:row r="2" ht="23" customHeight="1">
       <x:c r="A2" s="8" t="str">
@@ -554,6 +563,9 @@
       </x:c>
       <x:c r="B2" s="8"/>
       <x:c r="C2" s="8"/>
+      <x:c r="D2" s="8"/>
+      <x:c r="E2" s="8"/>
+      <x:c r="F2" s="8"/>
     </x:row>
     <x:row r="3" ht="25" customHeight="1">
       <x:c r="A3" s="17" t="str">
@@ -565,6 +577,15 @@
       <x:c r="C3" s="19" t="str">
         <x:v>טלפון</x:v>
       </x:c>
+      <x:c r="D3" s="19" t="str">
+        <x:v>עיסוק</x:v>
+      </x:c>
+      <x:c r="E3" s="19" t="str">
+        <x:v>איש/אשת קשר נוסף/ת</x:v>
+      </x:c>
+      <x:c r="F3" s="19" t="str">
+        <x:v>טלפון נוסף</x:v>
+      </x:c>
     </x:row>
     <x:row r="4" ht="23" customHeight="1">
       <x:c r="A4" s="51" t="n">
@@ -576,6 +597,9 @@
       <x:c r="C4" s="53" t="str">
         <x:v>‎052-375-3944</x:v>
       </x:c>
+      <x:c r="D4" s="53"/>
+      <x:c r="E4" s="53"/>
+      <x:c r="F4" s="53"/>
     </x:row>
     <x:row r="5" ht="23" customHeight="1">
       <x:c r="A5" s="40" t="n">
@@ -587,6 +611,9 @@
       <x:c r="C5" s="49" t="str">
         <x:v>‎052-381-5370</x:v>
       </x:c>
+      <x:c r="D5" s="49"/>
+      <x:c r="E5" s="49"/>
+      <x:c r="F5" s="49"/>
     </x:row>
     <x:row r="6" ht="23" customHeight="1">
       <x:c r="A6" s="54" t="n">
@@ -598,6 +625,9 @@
       <x:c r="C6" s="56" t="str">
         <x:v>‎052-284-6598</x:v>
       </x:c>
+      <x:c r="D6" s="56"/>
+      <x:c r="E6" s="56"/>
+      <x:c r="F6" s="56"/>
     </x:row>
     <x:row r="7" ht="23" customHeight="1">
       <x:c r="A7" s="40" t="n">
@@ -609,6 +639,9 @@
       <x:c r="C7" s="49" t="str">
         <x:v>‎050-431-4666</x:v>
       </x:c>
+      <x:c r="D7" s="49"/>
+      <x:c r="E7" s="49"/>
+      <x:c r="F7" s="49"/>
     </x:row>
     <x:row r="8" ht="23" customHeight="1">
       <x:c r="A8" s="54" t="n">
@@ -620,6 +653,9 @@
       <x:c r="C8" s="56" t="str">
         <x:v>‎052-565-6174</x:v>
       </x:c>
+      <x:c r="D8" s="56"/>
+      <x:c r="E8" s="56"/>
+      <x:c r="F8" s="56"/>
     </x:row>
     <x:row r="9" ht="23" customHeight="1">
       <x:c r="A9" s="40" t="n">
@@ -631,6 +667,9 @@
       <x:c r="C9" s="49" t="str">
         <x:v>‎054-634-1131</x:v>
       </x:c>
+      <x:c r="D9" s="49"/>
+      <x:c r="E9" s="49"/>
+      <x:c r="F9" s="49"/>
     </x:row>
     <x:row r="10" ht="23" customHeight="1">
       <x:c r="A10" s="54" t="n">
@@ -642,6 +681,9 @@
       <x:c r="C10" s="56" t="str">
         <x:v>‎052-225-4794</x:v>
       </x:c>
+      <x:c r="D10" s="56"/>
+      <x:c r="E10" s="56"/>
+      <x:c r="F10" s="56"/>
     </x:row>
     <x:row r="11" ht="23" customHeight="1">
       <x:c r="A11" s="40" t="n">
@@ -653,6 +695,9 @@
       <x:c r="C11" s="49" t="str">
         <x:v>‎054-665-1481</x:v>
       </x:c>
+      <x:c r="D11" s="49"/>
+      <x:c r="E11" s="49"/>
+      <x:c r="F11" s="49"/>
     </x:row>
     <x:row r="12" ht="23" customHeight="1">
       <x:c r="A12" s="54" t="n">
@@ -664,6 +709,9 @@
       <x:c r="C12" s="56" t="str">
         <x:v>‎053-374-3023</x:v>
       </x:c>
+      <x:c r="D12" s="56"/>
+      <x:c r="E12" s="56"/>
+      <x:c r="F12" s="56"/>
     </x:row>
     <x:row r="13" ht="23" customHeight="1">
       <x:c r="A13" s="40" t="n">
@@ -675,6 +723,9 @@
       <x:c r="C13" s="49" t="str">
         <x:v>‎050-321-4672</x:v>
       </x:c>
+      <x:c r="D13" s="49"/>
+      <x:c r="E13" s="49"/>
+      <x:c r="F13" s="49"/>
     </x:row>
     <x:row r="14" ht="23" customHeight="1">
       <x:c r="A14" s="54" t="n">
@@ -686,6 +737,9 @@
       <x:c r="C14" s="56" t="str">
         <x:v>‎053-246-5945</x:v>
       </x:c>
+      <x:c r="D14" s="56"/>
+      <x:c r="E14" s="56"/>
+      <x:c r="F14" s="56"/>
     </x:row>
     <x:row r="15" ht="23" customHeight="1">
       <x:c r="A15" s="40" t="n">
@@ -697,15 +751,25 @@
       <x:c r="C15" s="49" t="str">
         <x:v>‎052-235-2105</x:v>
       </x:c>
+      <x:c r="D15" s="49"/>
+      <x:c r="E15" s="49"/>
+      <x:c r="F15" s="49"/>
     </x:row>
     <x:row r="16" ht="23" customHeight="1">
       <x:c r="A16" s="54" t="n">
         <x:v>13</x:v>
       </x:c>
       <x:c r="B16" s="55" t="str">
-        <x:v>אבי שיוביץ (פאולה אלמוג)</x:v>
+        <x:v>פאולה אלמוג</x:v>
       </x:c>
       <x:c r="C16" s="56" t="str">
+        <x:v>‎052-809-8209</x:v>
+      </x:c>
+      <x:c r="D16" s="56"/>
+      <x:c r="E16" s="56" t="str">
+        <x:v>אבי שיוביץ</x:v>
+      </x:c>
+      <x:c r="F16" s="56" t="str">
         <x:v>‎054-222-8499</x:v>
       </x:c>
     </x:row>
@@ -719,6 +783,11 @@
       <x:c r="C17" s="49" t="str">
         <x:v>‎054-662-0031</x:v>
       </x:c>
+      <x:c r="D17" s="49" t="str">
+        <x:v>רואה חשבון</x:v>
+      </x:c>
+      <x:c r="E17" s="49"/>
+      <x:c r="F17" s="49"/>
     </x:row>
     <x:row r="18" ht="23" customHeight="1">
       <x:c r="A18" s="54" t="n">
@@ -730,6 +799,9 @@
       <x:c r="C18" s="56" t="str">
         <x:v>‎050-206-1431</x:v>
       </x:c>
+      <x:c r="D18" s="56"/>
+      <x:c r="E18" s="56"/>
+      <x:c r="F18" s="56"/>
     </x:row>
     <x:row r="19" ht="23" customHeight="1">
       <x:c r="A19" s="40" t="n">
@@ -741,6 +813,9 @@
       <x:c r="C19" s="49" t="str">
         <x:v>‎054-595-4570</x:v>
       </x:c>
+      <x:c r="D19" s="49"/>
+      <x:c r="E19" s="49"/>
+      <x:c r="F19" s="49"/>
     </x:row>
     <x:row r="20" ht="23" customHeight="1">
       <x:c r="A20" s="54" t="n">
@@ -752,6 +827,9 @@
       <x:c r="C20" s="56" t="str">
         <x:v>‎054-686-9960</x:v>
       </x:c>
+      <x:c r="D20" s="56"/>
+      <x:c r="E20" s="56"/>
+      <x:c r="F20" s="56"/>
     </x:row>
     <x:row r="21" ht="23" customHeight="1">
       <x:c r="A21" s="40" t="n">
@@ -763,6 +841,9 @@
       <x:c r="C21" s="49" t="str">
         <x:v>‎054-541-6261</x:v>
       </x:c>
+      <x:c r="D21" s="49"/>
+      <x:c r="E21" s="49"/>
+      <x:c r="F21" s="49"/>
     </x:row>
     <x:row r="22" ht="23" customHeight="1">
       <x:c r="A22" s="54" t="n">
@@ -774,6 +855,9 @@
       <x:c r="C22" s="56" t="str">
         <x:v>‎054-756-0688</x:v>
       </x:c>
+      <x:c r="D22" s="56"/>
+      <x:c r="E22" s="56"/>
+      <x:c r="F22" s="56"/>
     </x:row>
     <x:row r="23" ht="23" customHeight="1">
       <x:c r="A23" s="41" t="n">
@@ -785,15 +869,18 @@
       <x:c r="C23" s="50" t="str">
         <x:v>‎052-332-6597</x:v>
       </x:c>
+      <x:c r="D23" s="50"/>
+      <x:c r="E23" s="50"/>
+      <x:c r="F23" s="50"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
-    <x:mergeCell ref="A1:C1"/>
-    <x:mergeCell ref="A2:C2"/>
+    <x:mergeCell ref="A1:F1"/>
+    <x:mergeCell ref="A2:F2"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R999a9bc050d34a65"/>
+    <x:tablePart ns1:id="R999a9bc050d34a65"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/owners.xlsx
+++ b/owners.xlsx
@@ -8,7 +8,14 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="2" count="2">
+  <si>
+    <t>עודכן: 2026-07-07</t>
+  </si>
+  <si>
+    <t>ועד בית</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
@@ -536,351 +543,353 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:worksheet xmlns:ns1="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:sheetFormatPr defaultRowHeight="15"/>
-  <x:cols>
-    <x:col min="1" max="1" width="11" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="34" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="26" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="20" hidden="0" customWidth="1"/>
-  </x:cols>
-  <x:sheetData>
-    <x:row r="1" ht="34" customHeight="1">
-      <x:c r="A1" s="4" t="str">
-        <x:v>רשימת בעלי דירות</x:v>
-      </x:c>
-      <x:c r="B1" s="4"/>
-      <x:c r="C1" s="4"/>
-      <x:c r="D1" s="4"/>
-      <x:c r="E1" s="4"/>
-      <x:c r="F1" s="4"/>
-    </x:row>
-    <x:row r="2" ht="23" customHeight="1">
-      <x:c r="A2" s="8" t="str">
-        <x:v>עודכן: 2026-06-26</x:v>
-      </x:c>
-      <x:c r="B2" s="8"/>
-      <x:c r="C2" s="8"/>
-      <x:c r="D2" s="8"/>
-      <x:c r="E2" s="8"/>
-      <x:c r="F2" s="8"/>
-    </x:row>
-    <x:row r="3" ht="25" customHeight="1">
-      <x:c r="A3" s="17" t="str">
-        <x:v>דירה</x:v>
-      </x:c>
-      <x:c r="B3" s="18" t="str">
-        <x:v>שם</x:v>
-      </x:c>
-      <x:c r="C3" s="19" t="str">
-        <x:v>טלפון</x:v>
-      </x:c>
-      <x:c r="D3" s="19" t="str">
-        <x:v>עיסוק</x:v>
-      </x:c>
-      <x:c r="E3" s="19" t="str">
-        <x:v>איש/אשת קשר נוסף/ת</x:v>
-      </x:c>
-      <x:c r="F3" s="19" t="str">
-        <x:v>טלפון נוסף</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4" ht="23" customHeight="1">
-      <x:c r="A4" s="51" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="B4" s="52" t="str">
-        <x:v>פל נלי</x:v>
-      </x:c>
-      <x:c r="C4" s="53" t="str">
-        <x:v>‎052-375-3944</x:v>
-      </x:c>
-      <x:c r="D4" s="53"/>
-      <x:c r="E4" s="53"/>
-      <x:c r="F4" s="53"/>
-    </x:row>
-    <x:row r="5" ht="23" customHeight="1">
-      <x:c r="A5" s="40" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="B5" s="43" t="str">
-        <x:v>שוהם פרנקל (קרן שמש)</x:v>
-      </x:c>
-      <x:c r="C5" s="49" t="str">
-        <x:v>‎052-381-5370</x:v>
-      </x:c>
-      <x:c r="D5" s="49"/>
-      <x:c r="E5" s="49"/>
-      <x:c r="F5" s="49"/>
-    </x:row>
-    <x:row r="6" ht="23" customHeight="1">
-      <x:c r="A6" s="54" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="B6" s="55" t="str">
-        <x:v>גדי גדות</x:v>
-      </x:c>
-      <x:c r="C6" s="56" t="str">
-        <x:v>‎052-284-6598</x:v>
-      </x:c>
-      <x:c r="D6" s="56"/>
-      <x:c r="E6" s="56"/>
-      <x:c r="F6" s="56"/>
-    </x:row>
-    <x:row r="7" ht="23" customHeight="1">
-      <x:c r="A7" s="40" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="B7" s="43" t="str">
-        <x:v>עדי גולד</x:v>
-      </x:c>
-      <x:c r="C7" s="49" t="str">
-        <x:v>‎050-431-4666</x:v>
-      </x:c>
-      <x:c r="D7" s="49"/>
-      <x:c r="E7" s="49"/>
-      <x:c r="F7" s="49"/>
-    </x:row>
-    <x:row r="8" ht="23" customHeight="1">
-      <x:c r="A8" s="54" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="B8" s="55" t="str">
-        <x:v>אברמוב גבי</x:v>
-      </x:c>
-      <x:c r="C8" s="56" t="str">
-        <x:v>‎052-565-6174</x:v>
-      </x:c>
-      <x:c r="D8" s="56"/>
-      <x:c r="E8" s="56"/>
-      <x:c r="F8" s="56"/>
-    </x:row>
-    <x:row r="9" ht="23" customHeight="1">
-      <x:c r="A9" s="40" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="B9" s="43" t="str">
-        <x:v>הדר שיילובסקי</x:v>
-      </x:c>
-      <x:c r="C9" s="49" t="str">
-        <x:v>‎054-634-1131</x:v>
-      </x:c>
-      <x:c r="D9" s="49"/>
-      <x:c r="E9" s="49"/>
-      <x:c r="F9" s="49"/>
-    </x:row>
-    <x:row r="10" ht="23" customHeight="1">
-      <x:c r="A10" s="54" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="B10" s="55" t="str">
-        <x:v>מור תורג'מן</x:v>
-      </x:c>
-      <x:c r="C10" s="56" t="str">
-        <x:v>‎052-225-4794</x:v>
-      </x:c>
-      <x:c r="D10" s="56"/>
-      <x:c r="E10" s="56"/>
-      <x:c r="F10" s="56"/>
-    </x:row>
-    <x:row r="11" ht="23" customHeight="1">
-      <x:c r="A11" s="40" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="B11" s="43" t="str">
-        <x:v>טארק אריק</x:v>
-      </x:c>
-      <x:c r="C11" s="49" t="str">
-        <x:v>‎054-665-1481</x:v>
-      </x:c>
-      <x:c r="D11" s="49"/>
-      <x:c r="E11" s="49"/>
-      <x:c r="F11" s="49"/>
-    </x:row>
-    <x:row r="12" ht="23" customHeight="1">
-      <x:c r="A12" s="54" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="B12" s="55" t="str">
-        <x:v>תמר מזור (רוזנר)</x:v>
-      </x:c>
-      <x:c r="C12" s="56" t="str">
-        <x:v>‎053-374-3023</x:v>
-      </x:c>
-      <x:c r="D12" s="56"/>
-      <x:c r="E12" s="56"/>
-      <x:c r="F12" s="56"/>
-    </x:row>
-    <x:row r="13" ht="23" customHeight="1">
-      <x:c r="A13" s="40" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="B13" s="43" t="str">
-        <x:v>חביבה גרינברג (משה חנה)</x:v>
-      </x:c>
-      <x:c r="C13" s="49" t="str">
-        <x:v>‎050-321-4672</x:v>
-      </x:c>
-      <x:c r="D13" s="49"/>
-      <x:c r="E13" s="49"/>
-      <x:c r="F13" s="49"/>
-    </x:row>
-    <x:row r="14" ht="23" customHeight="1">
-      <x:c r="A14" s="54" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="B14" s="55" t="str">
-        <x:v>יבגני גרינברג</x:v>
-      </x:c>
-      <x:c r="C14" s="56" t="str">
-        <x:v>‎053-246-5945</x:v>
-      </x:c>
-      <x:c r="D14" s="56"/>
-      <x:c r="E14" s="56"/>
-      <x:c r="F14" s="56"/>
-    </x:row>
-    <x:row r="15" ht="23" customHeight="1">
-      <x:c r="A15" s="40" t="n">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="B15" s="43" t="str">
-        <x:v>גבאי אלכס</x:v>
-      </x:c>
-      <x:c r="C15" s="49" t="str">
-        <x:v>‎052-235-2105</x:v>
-      </x:c>
-      <x:c r="D15" s="49"/>
-      <x:c r="E15" s="49"/>
-      <x:c r="F15" s="49"/>
-    </x:row>
-    <x:row r="16" ht="23" customHeight="1">
-      <x:c r="A16" s="54" t="n">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="B16" s="55" t="str">
-        <x:v>פאולה אלמוג</x:v>
-      </x:c>
-      <x:c r="C16" s="56" t="str">
-        <x:v>‎052-809-8209</x:v>
-      </x:c>
-      <x:c r="D16" s="56"/>
-      <x:c r="E16" s="56" t="str">
-        <x:v>אבי שיוביץ</x:v>
-      </x:c>
-      <x:c r="F16" s="56" t="str">
-        <x:v>‎054-222-8499</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="17" ht="23" customHeight="1">
-      <x:c r="A17" s="40" t="n">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="B17" s="43" t="str">
-        <x:v>מולהם גבאלי</x:v>
-      </x:c>
-      <x:c r="C17" s="49" t="str">
-        <x:v>‎054-662-0031</x:v>
-      </x:c>
-      <x:c r="D17" s="49" t="str">
-        <x:v>רואה חשבון</x:v>
-      </x:c>
-      <x:c r="E17" s="49"/>
-      <x:c r="F17" s="49"/>
-    </x:row>
-    <x:row r="18" ht="23" customHeight="1">
-      <x:c r="A18" s="54" t="n">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="B18" s="55" t="str">
-        <x:v>אירינה שרמן</x:v>
-      </x:c>
-      <x:c r="C18" s="56" t="str">
-        <x:v>‎050-206-1431</x:v>
-      </x:c>
-      <x:c r="D18" s="56"/>
-      <x:c r="E18" s="56"/>
-      <x:c r="F18" s="56"/>
-    </x:row>
-    <x:row r="19" ht="23" customHeight="1">
-      <x:c r="A19" s="40" t="n">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="B19" s="43" t="str">
-        <x:v>רונית קלמנוביץ דיקשטין</x:v>
-      </x:c>
-      <x:c r="C19" s="49" t="str">
-        <x:v>‎054-595-4570</x:v>
-      </x:c>
-      <x:c r="D19" s="49"/>
-      <x:c r="E19" s="49"/>
-      <x:c r="F19" s="49"/>
-    </x:row>
-    <x:row r="20" ht="23" customHeight="1">
-      <x:c r="A20" s="54" t="n">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="B20" s="55" t="str">
-        <x:v>עדן טאטור</x:v>
-      </x:c>
-      <x:c r="C20" s="56" t="str">
-        <x:v>‎054-686-9960</x:v>
-      </x:c>
-      <x:c r="D20" s="56"/>
-      <x:c r="E20" s="56"/>
-      <x:c r="F20" s="56"/>
-    </x:row>
-    <x:row r="21" ht="23" customHeight="1">
-      <x:c r="A21" s="40" t="n">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="B21" s="43" t="str">
-        <x:v>דן ולדסקי</x:v>
-      </x:c>
-      <x:c r="C21" s="49" t="str">
-        <x:v>‎054-541-6261</x:v>
-      </x:c>
-      <x:c r="D21" s="49"/>
-      <x:c r="E21" s="49"/>
-      <x:c r="F21" s="49"/>
-    </x:row>
-    <x:row r="22" ht="23" customHeight="1">
-      <x:c r="A22" s="54" t="n">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="B22" s="55" t="str">
-        <x:v>נואל רוחאנה</x:v>
-      </x:c>
-      <x:c r="C22" s="56" t="str">
-        <x:v>‎054-756-0688</x:v>
-      </x:c>
-      <x:c r="D22" s="56"/>
-      <x:c r="E22" s="56"/>
-      <x:c r="F22" s="56"/>
-    </x:row>
-    <x:row r="23" ht="23" customHeight="1">
-      <x:c r="A23" s="41" t="n">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="B23" s="44" t="str">
-        <x:v>מארון פרחאת</x:v>
-      </x:c>
-      <x:c r="C23" s="50" t="str">
-        <x:v>‎052-332-6597</x:v>
-      </x:c>
-      <x:c r="D23" s="50"/>
-      <x:c r="E23" s="50"/>
-      <x:c r="F23" s="50"/>
-    </x:row>
-  </x:sheetData>
-  <x:mergeCells>
-    <x:mergeCell ref="A1:F1"/>
-    <x:mergeCell ref="A2:F2"/>
-  </x:mergeCells>
-  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:tableParts count="1">
-    <x:tablePart ns1:id="R999a9bc050d34a65"/>
-  </x:tableParts>
-</x:worksheet>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="11" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="34" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <col min="4" max="4" width="18" hidden="0" customWidth="1"/>
+    <col min="5" max="5" width="26" hidden="0" customWidth="1"/>
+    <col min="6" max="6" width="20" hidden="0" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="34" customHeight="1">
+      <c r="A1" s="4" t="str">
+        <v>רשימת בעלי דירות</v>
+      </c>
+      <c r="B1" s="4"/>
+      <c r="C1" s="4"/>
+      <c r="D1" s="4"/>
+      <c r="E1" s="4"/>
+      <c r="F1" s="4"/>
+    </row>
+    <row r="2" ht="23" customHeight="1">
+      <c r="A2" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="8"/>
+      <c r="C2" s="8"/>
+      <c r="D2" s="8"/>
+      <c r="E2" s="8"/>
+      <c r="F2" s="8"/>
+    </row>
+    <row r="3" ht="25" customHeight="1">
+      <c r="A3" s="17" t="str">
+        <v>דירה</v>
+      </c>
+      <c r="B3" s="18" t="str">
+        <v>שם</v>
+      </c>
+      <c r="C3" s="19" t="str">
+        <v>טלפון</v>
+      </c>
+      <c r="D3" s="19" t="str">
+        <v>עיסוק</v>
+      </c>
+      <c r="E3" s="19" t="str">
+        <v>איש/אשת קשר נוסף/ת</v>
+      </c>
+      <c r="F3" s="19" t="str">
+        <v>טלפון נוסף</v>
+      </c>
+    </row>
+    <row r="4" ht="23" customHeight="1">
+      <c r="A4" s="51" t="n">
+        <v>1</v>
+      </c>
+      <c r="B4" s="52" t="str">
+        <v>פל נלי</v>
+      </c>
+      <c r="C4" s="53" t="str">
+        <v>‎052-375-3944</v>
+      </c>
+      <c r="D4" s="53"/>
+      <c r="E4" s="53"/>
+      <c r="F4" s="53"/>
+    </row>
+    <row r="5" ht="23" customHeight="1">
+      <c r="A5" s="40" t="n">
+        <v>2</v>
+      </c>
+      <c r="B5" s="43" t="str">
+        <v>שוהם פרנקל (קרן שמש)</v>
+      </c>
+      <c r="C5" s="49" t="str">
+        <v>‎052-381-5370</v>
+      </c>
+      <c r="D5" s="49"/>
+      <c r="E5" s="49"/>
+      <c r="F5" s="49"/>
+    </row>
+    <row r="6" ht="23" customHeight="1">
+      <c r="A6" s="54" t="n">
+        <v>3</v>
+      </c>
+      <c r="B6" s="55" t="str">
+        <v>גדי גדות</v>
+      </c>
+      <c r="C6" s="56" t="str">
+        <v>‎052-284-6598</v>
+      </c>
+      <c r="D6" s="56"/>
+      <c r="E6" s="56"/>
+      <c r="F6" s="56"/>
+    </row>
+    <row r="7" ht="23" customHeight="1">
+      <c r="A7" s="40" t="n">
+        <v>4</v>
+      </c>
+      <c r="B7" s="43" t="str">
+        <v>עדי גולד</v>
+      </c>
+      <c r="C7" s="49" t="str">
+        <v>‎050-431-4666</v>
+      </c>
+      <c r="D7" s="49"/>
+      <c r="E7" s="49"/>
+      <c r="F7" s="49"/>
+    </row>
+    <row r="8" ht="23" customHeight="1">
+      <c r="A8" s="54" t="n">
+        <v>5</v>
+      </c>
+      <c r="B8" s="55" t="str">
+        <v>אברמוב גבי</v>
+      </c>
+      <c r="C8" s="56" t="str">
+        <v>‎052-565-6174</v>
+      </c>
+      <c r="D8" s="56"/>
+      <c r="E8" s="56"/>
+      <c r="F8" s="56"/>
+    </row>
+    <row r="9" ht="23" customHeight="1">
+      <c r="A9" s="40" t="n">
+        <v>6</v>
+      </c>
+      <c r="B9" s="43" t="str">
+        <v>הדר שיילובסקי</v>
+      </c>
+      <c r="C9" s="49" t="str">
+        <v>‎054-634-1131</v>
+      </c>
+      <c r="D9" s="49"/>
+      <c r="E9" s="49"/>
+      <c r="F9" s="49"/>
+    </row>
+    <row r="10" ht="23" customHeight="1">
+      <c r="A10" s="54" t="n">
+        <v>7</v>
+      </c>
+      <c r="B10" s="55" t="str">
+        <v>מור תורג'מן</v>
+      </c>
+      <c r="C10" s="56" t="str">
+        <v>‎052-225-4794</v>
+      </c>
+      <c r="D10" s="56"/>
+      <c r="E10" s="56"/>
+      <c r="F10" s="56"/>
+    </row>
+    <row r="11" ht="23" customHeight="1">
+      <c r="A11" s="40" t="n">
+        <v>8</v>
+      </c>
+      <c r="B11" s="43" t="str">
+        <v>טארק אריק</v>
+      </c>
+      <c r="C11" s="49" t="str">
+        <v>‎054-665-1481</v>
+      </c>
+      <c r="D11" s="49"/>
+      <c r="E11" s="49"/>
+      <c r="F11" s="49"/>
+    </row>
+    <row r="12" ht="23" customHeight="1">
+      <c r="A12" s="54" t="n">
+        <v>9</v>
+      </c>
+      <c r="B12" s="55" t="str">
+        <v>תמר מזור (רוזנר)</v>
+      </c>
+      <c r="C12" s="56" t="str">
+        <v>‎053-374-3023</v>
+      </c>
+      <c r="D12" s="56"/>
+      <c r="E12" s="56"/>
+      <c r="F12" s="56"/>
+    </row>
+    <row r="13" ht="23" customHeight="1">
+      <c r="A13" s="40" t="n">
+        <v>10</v>
+      </c>
+      <c r="B13" s="43" t="str">
+        <v>חביבה גרינברג (משה חנה)</v>
+      </c>
+      <c r="C13" s="49" t="str">
+        <v>‎050-321-4672</v>
+      </c>
+      <c r="D13" s="49"/>
+      <c r="E13" s="49"/>
+      <c r="F13" s="49"/>
+    </row>
+    <row r="14" ht="23" customHeight="1">
+      <c r="A14" s="54" t="n">
+        <v>11</v>
+      </c>
+      <c r="B14" s="55" t="str">
+        <v>יבגני גרינברג</v>
+      </c>
+      <c r="C14" s="56" t="str">
+        <v>‎053-246-5945</v>
+      </c>
+      <c r="D14" s="56"/>
+      <c r="E14" s="56"/>
+      <c r="F14" s="56"/>
+    </row>
+    <row r="15" ht="23" customHeight="1">
+      <c r="A15" s="40" t="n">
+        <v>12</v>
+      </c>
+      <c r="B15" s="43" t="str">
+        <v>גבאי אלכס</v>
+      </c>
+      <c r="C15" s="49" t="str">
+        <v>‎052-235-2105</v>
+      </c>
+      <c r="D15" s="49"/>
+      <c r="E15" s="49"/>
+      <c r="F15" s="49"/>
+    </row>
+    <row r="16" ht="23" customHeight="1">
+      <c r="A16" s="54" t="n">
+        <v>13</v>
+      </c>
+      <c r="B16" s="55" t="str">
+        <v>פאולה אלמוג</v>
+      </c>
+      <c r="C16" s="56" t="str">
+        <v>‎052-809-8209</v>
+      </c>
+      <c r="D16" s="56"/>
+      <c r="E16" s="56" t="str">
+        <v>אבי שיוביץ</v>
+      </c>
+      <c r="F16" s="56" t="str">
+        <v>‎054-222-8499</v>
+      </c>
+    </row>
+    <row r="17" ht="23" customHeight="1">
+      <c r="A17" s="40" t="n">
+        <v>14</v>
+      </c>
+      <c r="B17" s="43" t="str">
+        <v>מולהם גבאלי</v>
+      </c>
+      <c r="C17" s="49" t="str">
+        <v>‎054-662-0031</v>
+      </c>
+      <c r="D17" s="49" t="str">
+        <v>רואה חשבון</v>
+      </c>
+      <c r="E17" s="49"/>
+      <c r="F17" s="49"/>
+    </row>
+    <row r="18" ht="23" customHeight="1">
+      <c r="A18" s="54" t="n">
+        <v>15</v>
+      </c>
+      <c r="B18" s="55" t="str">
+        <v>אירינה שרמן</v>
+      </c>
+      <c r="C18" s="56" t="str">
+        <v>‎050-206-1431</v>
+      </c>
+      <c r="D18" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="E18" s="56"/>
+      <c r="F18" s="56"/>
+    </row>
+    <row r="19" ht="23" customHeight="1">
+      <c r="A19" s="40" t="n">
+        <v>16</v>
+      </c>
+      <c r="B19" s="43" t="str">
+        <v>רונית קלמנוביץ דיקשטין</v>
+      </c>
+      <c r="C19" s="49" t="str">
+        <v>‎054-595-4570</v>
+      </c>
+      <c r="D19" s="49"/>
+      <c r="E19" s="49"/>
+      <c r="F19" s="49"/>
+    </row>
+    <row r="20" ht="23" customHeight="1">
+      <c r="A20" s="54" t="n">
+        <v>17</v>
+      </c>
+      <c r="B20" s="55" t="str">
+        <v>עדן טאטור</v>
+      </c>
+      <c r="C20" s="56" t="str">
+        <v>‎054-686-9960</v>
+      </c>
+      <c r="D20" s="56"/>
+      <c r="E20" s="56"/>
+      <c r="F20" s="56"/>
+    </row>
+    <row r="21" ht="23" customHeight="1">
+      <c r="A21" s="40" t="n">
+        <v>18</v>
+      </c>
+      <c r="B21" s="43" t="str">
+        <v>דן ולדסקי</v>
+      </c>
+      <c r="C21" s="49" t="str">
+        <v>‎054-541-6261</v>
+      </c>
+      <c r="D21" s="49"/>
+      <c r="E21" s="49"/>
+      <c r="F21" s="49"/>
+    </row>
+    <row r="22" ht="23" customHeight="1">
+      <c r="A22" s="54" t="n">
+        <v>19</v>
+      </c>
+      <c r="B22" s="55" t="str">
+        <v>נואל רוחאנה</v>
+      </c>
+      <c r="C22" s="56" t="str">
+        <v>‎054-756-0688</v>
+      </c>
+      <c r="D22" s="56"/>
+      <c r="E22" s="56"/>
+      <c r="F22" s="56"/>
+    </row>
+    <row r="23" ht="23" customHeight="1">
+      <c r="A23" s="41" t="n">
+        <v>20</v>
+      </c>
+      <c r="B23" s="44" t="str">
+        <v>מארון פרחאת</v>
+      </c>
+      <c r="C23" s="50" t="str">
+        <v>‎052-332-6597</v>
+      </c>
+      <c r="D23" s="50"/>
+      <c r="E23" s="50"/>
+      <c r="F23" s="50"/>
+    </row>
+  </sheetData>
+  <mergeCells>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A2:F2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart ns1:id="R999a9bc050d34a65"/>
+  </tableParts>
+</worksheet>
 </file>
--- a/owners.xlsx
+++ b/owners.xlsx
@@ -10,7 +10,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="2" count="2">
   <si>
-    <t>עודכן: 2026-07-07</t>
+    <t>עודכן: 2026-07-30</t>
   </si>
   <si>
     <t>ועד בית</t>
@@ -599,14 +599,18 @@
         <v>1</v>
       </c>
       <c r="B4" s="52" t="str">
-        <v>פל נלי</v>
+        <v>פל נלי; אריאל</v>
       </c>
       <c r="C4" s="53" t="str">
         <v>‎052-375-3944</v>
       </c>
       <c r="D4" s="53"/>
-      <c r="E4" s="53"/>
-      <c r="F4" s="53"/>
+      <c r="E4" s="53" t="str">
+        <v>אריאל</v>
+      </c>
+      <c r="F4" s="53" t="str">
+        <v>‎052-436-9553</v>
+      </c>
     </row>
     <row r="5" ht="23" customHeight="1">
       <c r="A5" s="40" t="n">

--- a/owners.xlsx
+++ b/owners.xlsx
@@ -10,7 +10,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="2" count="2">
   <si>
-    <t>עודכן: 2026-07-30</t>
+    <t>עודכן: 2026-08-06</t>
   </si>
   <si>
     <t>ועד בית</t>
@@ -827,8 +827,12 @@
         <v>‎054-595-4570</v>
       </c>
       <c r="D19" s="49"/>
-      <c r="E19" s="49"/>
-      <c r="F19" s="49"/>
+      <c r="E19" s="49" t="str">
+        <v>יגאל קלמנוביץ</v>
+      </c>
+      <c r="F19" s="49" t="str">
+        <v>‎054-783-8694</v>
+      </c>
     </row>
     <row r="20" ht="23" customHeight="1">
       <c r="A20" s="54" t="n">
